--- a/Team-Data/2014-15/3-6-2014-15.xlsx
+++ b/Team-Data/2014-15/3-6-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,22 +728,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F2" t="n">
         <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>0.803</v>
+        <v>0.8</v>
       </c>
       <c r="H2" t="n">
         <v>48.2</v>
       </c>
       <c r="I2" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J2" t="n">
         <v>81.09999999999999</v>
@@ -688,31 +755,31 @@
         <v>9.9</v>
       </c>
       <c r="M2" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="N2" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O2" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P2" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.777</v>
+        <v>0.776</v>
       </c>
       <c r="R2" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T2" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U2" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="V2" t="n">
         <v>14.4</v>
@@ -727,19 +794,19 @@
         <v>4.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>102.7</v>
+        <v>102.6</v>
       </c>
       <c r="AC2" t="n">
         <v>6.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -751,10 +818,10 @@
         <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ2" t="n">
         <v>26</v>
@@ -784,7 +851,7 @@
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AT2" t="n">
         <v>27</v>
@@ -796,10 +863,10 @@
         <v>17</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY2" t="n">
         <v>15</v>
@@ -808,7 +875,7 @@
         <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB2" t="n">
         <v>8</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -843,55 +910,55 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
         <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>0.417</v>
+        <v>0.407</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J3" t="n">
-        <v>88.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L3" t="n">
         <v>8</v>
       </c>
       <c r="M3" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.33</v>
+        <v>0.328</v>
       </c>
       <c r="O3" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="P3" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.752</v>
+        <v>0.749</v>
       </c>
       <c r="R3" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S3" t="n">
         <v>32.8</v>
       </c>
       <c r="T3" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="U3" t="n">
         <v>24.4</v>
@@ -909,31 +976,31 @@
         <v>5.5</v>
       </c>
       <c r="Z3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE3" t="n">
         <v>21</v>
       </c>
-      <c r="AA3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>101</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="AD3" t="n">
+      <c r="AF3" t="n">
         <v>21</v>
       </c>
-      <c r="AE3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>20</v>
-      </c>
       <c r="AG3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI3" t="n">
         <v>5</v>
@@ -951,7 +1018,7 @@
         <v>12</v>
       </c>
       <c r="AN3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
         <v>28</v>
@@ -969,13 +1036,13 @@
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU3" t="n">
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
         <v>11</v>
@@ -993,10 +1060,10 @@
         <v>29</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" t="n">
         <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>0.417</v>
+        <v>0.424</v>
       </c>
       <c r="H4" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J4" t="n">
-        <v>82.3</v>
+        <v>82</v>
       </c>
       <c r="K4" t="n">
-        <v>0.446</v>
+        <v>0.448</v>
       </c>
       <c r="L4" t="n">
         <v>6.6</v>
@@ -1055,73 +1122,73 @@
         <v>20.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.324</v>
+        <v>0.323</v>
       </c>
       <c r="O4" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P4" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.748</v>
+        <v>0.746</v>
       </c>
       <c r="R4" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S4" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T4" t="n">
-        <v>42.4</v>
+        <v>42.1</v>
       </c>
       <c r="U4" t="n">
         <v>20.4</v>
       </c>
       <c r="V4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W4" t="n">
         <v>6.9</v>
       </c>
       <c r="X4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y4" t="n">
         <v>4.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.4</v>
+        <v>-3.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
         <v>20</v>
       </c>
       <c r="AF4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG4" t="n">
         <v>20</v>
       </c>
       <c r="AH4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="n">
         <v>20</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
@@ -1136,7 +1203,7 @@
         <v>27</v>
       </c>
       <c r="AO4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP4" t="n">
         <v>20</v>
@@ -1145,19 +1212,19 @@
         <v>19</v>
       </c>
       <c r="AR4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS4" t="n">
         <v>17</v>
       </c>
       <c r="AT4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
         <v>24</v>
@@ -1169,7 +1236,7 @@
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
         <v>17</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -1207,28 +1274,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
         <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>0.45</v>
+        <v>0.441</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J5" t="n">
         <v>84.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.427</v>
+        <v>0.426</v>
       </c>
       <c r="L5" t="n">
         <v>5.8</v>
@@ -1237,7 +1304,7 @@
         <v>18.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.315</v>
+        <v>0.316</v>
       </c>
       <c r="O5" t="n">
         <v>17.1</v>
@@ -1246,22 +1313,22 @@
         <v>23.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.74</v>
+        <v>0.738</v>
       </c>
       <c r="R5" t="n">
         <v>10.1</v>
       </c>
       <c r="S5" t="n">
-        <v>34.2</v>
+        <v>34</v>
       </c>
       <c r="T5" t="n">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="U5" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V5" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="W5" t="n">
         <v>6</v>
@@ -1273,31 +1340,31 @@
         <v>5.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AA5" t="n">
         <v>21.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.7</v>
+        <v>-1.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
         <v>26</v>
@@ -1336,10 +1403,10 @@
         <v>9</v>
       </c>
       <c r="AU5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
         <v>30</v>
@@ -1348,7 +1415,7 @@
         <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ5" t="n">
         <v>5</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E6" t="n">
         <v>39</v>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G6" t="n">
-        <v>0.619</v>
+        <v>0.629</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L6" t="n">
         <v>7.7</v>
@@ -1419,22 +1486,22 @@
         <v>21.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O6" t="n">
         <v>20.2</v>
       </c>
       <c r="P6" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.785</v>
+        <v>0.784</v>
       </c>
       <c r="R6" t="n">
         <v>12.3</v>
       </c>
       <c r="S6" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="T6" t="n">
         <v>46</v>
@@ -1452,43 +1519,43 @@
         <v>6.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AA6" t="n">
         <v>21.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>101</v>
+        <v>101.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
         <v>8</v>
       </c>
       <c r="AF6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG6" t="n">
         <v>8</v>
       </c>
       <c r="AH6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
         <v>14</v>
@@ -1497,19 +1564,19 @@
         <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
       </c>
       <c r="AP6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>3</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>2</v>
-      </c>
       <c r="AR6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS6" t="n">
         <v>7</v>
@@ -1530,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ6" t="n">
         <v>2</v>
@@ -1539,10 +1606,10 @@
         <v>3</v>
       </c>
       <c r="BB6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -1571,82 +1638,82 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E7" t="n">
         <v>39</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G7" t="n">
-        <v>0.609</v>
+        <v>0.619</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="J7" t="n">
-        <v>82.3</v>
+        <v>82.5</v>
       </c>
       <c r="K7" t="n">
         <v>0.456</v>
       </c>
       <c r="L7" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="M7" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="N7" t="n">
         <v>0.354</v>
       </c>
       <c r="O7" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P7" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.754</v>
+        <v>0.753</v>
       </c>
       <c r="R7" t="n">
         <v>11.3</v>
       </c>
       <c r="S7" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U7" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V7" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W7" t="n">
         <v>7.4</v>
       </c>
       <c r="X7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y7" t="n">
         <v>4.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AA7" t="n">
         <v>20.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>102.7</v>
+        <v>102.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
@@ -1658,19 +1725,19 @@
         <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH7" t="n">
         <v>28</v>
       </c>
       <c r="AI7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
@@ -1679,13 +1746,13 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO7" t="n">
         <v>6</v>
       </c>
       <c r="AP7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
         <v>17</v>
@@ -1694,16 +1761,16 @@
         <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AT7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU7" t="n">
         <v>11</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
         <v>17</v>
@@ -1724,7 +1791,7 @@
         <v>7</v>
       </c>
       <c r="BC7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -1768,13 +1835,13 @@
         <v>48.5</v>
       </c>
       <c r="I8" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="J8" t="n">
-        <v>85.8</v>
+        <v>85.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0.459</v>
+        <v>0.461</v>
       </c>
       <c r="L8" t="n">
         <v>9.300000000000001</v>
@@ -1783,22 +1850,22 @@
         <v>26.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O8" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P8" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R8" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S8" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T8" t="n">
         <v>42.3</v>
@@ -1807,31 +1874,31 @@
         <v>22.5</v>
       </c>
       <c r="V8" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="W8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X8" t="n">
         <v>4.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z8" t="n">
         <v>19.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.6</v>
+        <v>104.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>6</v>
@@ -1849,37 +1916,37 @@
         <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM8" t="n">
         <v>6</v>
       </c>
       <c r="AN8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO8" t="n">
         <v>21</v>
       </c>
       <c r="AP8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS8" t="n">
         <v>23</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>20</v>
-      </c>
       <c r="AT8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1900,7 +1967,7 @@
         <v>12</v>
       </c>
       <c r="BA8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -1935,37 +2002,37 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
         <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G9" t="n">
-        <v>0.355</v>
+        <v>0.361</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
       </c>
       <c r="I9" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J9" t="n">
         <v>86.59999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.429</v>
+        <v>0.427</v>
       </c>
       <c r="L9" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M9" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.314</v>
+        <v>0.313</v>
       </c>
       <c r="O9" t="n">
         <v>17.9</v>
@@ -1974,19 +2041,19 @@
         <v>24.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.732</v>
+        <v>0.733</v>
       </c>
       <c r="R9" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S9" t="n">
         <v>32.5</v>
       </c>
       <c r="T9" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="U9" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V9" t="n">
         <v>14.1</v>
@@ -1995,10 +2062,10 @@
         <v>7.4</v>
       </c>
       <c r="X9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z9" t="n">
         <v>22.8</v>
@@ -2007,13 +2074,13 @@
         <v>20.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>99.7</v>
+        <v>99.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>-4.3</v>
+        <v>-4.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2031,10 +2098,10 @@
         <v>18</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL9" t="n">
         <v>15</v>
@@ -2049,22 +2116,22 @@
         <v>9</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
         <v>24</v>
       </c>
       <c r="AR9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AS9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV9" t="n">
         <v>13</v>
@@ -2073,19 +2140,19 @@
         <v>18</v>
       </c>
       <c r="AX9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ9" t="n">
         <v>30</v>
       </c>
       <c r="BA9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC9" t="n">
         <v>25</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>0.377</v>
+        <v>0.383</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
@@ -2135,31 +2202,31 @@
         <v>36.7</v>
       </c>
       <c r="J10" t="n">
-        <v>85.90000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.427</v>
+        <v>0.428</v>
       </c>
       <c r="L10" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="M10" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0.338</v>
+        <v>0.341</v>
       </c>
       <c r="O10" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P10" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.705</v>
+        <v>0.704</v>
       </c>
       <c r="R10" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="S10" t="n">
         <v>32.6</v>
@@ -2183,19 +2250,19 @@
         <v>5.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AA10" t="n">
         <v>20</v>
       </c>
       <c r="AB10" t="n">
-        <v>98.2</v>
+        <v>98.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,16 +2274,16 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AK10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL10" t="n">
         <v>10</v>
@@ -2225,10 +2292,10 @@
         <v>10</v>
       </c>
       <c r="AN10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO10" t="n">
         <v>20</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>23</v>
       </c>
       <c r="AP10" t="n">
         <v>14</v>
@@ -2252,25 +2319,25 @@
         <v>8</v>
       </c>
       <c r="AW10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY10" t="n">
         <v>18</v>
       </c>
       <c r="AZ10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB10" t="n">
         <v>20</v>
       </c>
       <c r="BC10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F11" t="n">
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8</v>
+        <v>0.797</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="J11" t="n">
-        <v>87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="K11" t="n">
         <v>0.477</v>
@@ -2326,10 +2393,10 @@
         <v>10.7</v>
       </c>
       <c r="M11" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.39</v>
+        <v>0.389</v>
       </c>
       <c r="O11" t="n">
         <v>16.2</v>
@@ -2338,28 +2405,28 @@
         <v>21.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.769</v>
+        <v>0.767</v>
       </c>
       <c r="R11" t="n">
         <v>10.4</v>
       </c>
       <c r="S11" t="n">
-        <v>34.6</v>
+        <v>34.4</v>
       </c>
       <c r="T11" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="U11" t="n">
         <v>27.2</v>
       </c>
       <c r="V11" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W11" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="X11" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Y11" t="n">
         <v>3.4</v>
@@ -2371,13 +2438,13 @@
         <v>18.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>109.9</v>
+        <v>110</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2416,13 +2483,13 @@
         <v>25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR11" t="n">
         <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT11" t="n">
         <v>6</v>
@@ -2431,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW11" t="n">
         <v>4</v>
@@ -2443,10 +2510,10 @@
         <v>2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -2496,70 +2563,70 @@
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J12" t="n">
-        <v>84.3</v>
+        <v>84</v>
       </c>
       <c r="K12" t="n">
         <v>0.439</v>
       </c>
       <c r="L12" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="M12" t="n">
         <v>33.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.345</v>
+        <v>0.348</v>
       </c>
       <c r="O12" t="n">
-        <v>17.3</v>
+        <v>17.6</v>
       </c>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.721</v>
+        <v>0.718</v>
       </c>
       <c r="R12" t="n">
         <v>12.1</v>
       </c>
       <c r="S12" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="T12" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U12" t="n">
         <v>22</v>
       </c>
       <c r="V12" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="W12" t="n">
         <v>9.6</v>
       </c>
       <c r="X12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y12" t="n">
         <v>5.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>103</v>
+        <v>103.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2571,16 +2638,16 @@
         <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
         <v>19</v>
       </c>
       <c r="AJ12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
@@ -2589,16 +2656,16 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
         <v>12</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR12" t="n">
         <v>6</v>
@@ -2607,7 +2674,7 @@
         <v>24</v>
       </c>
       <c r="AT12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU12" t="n">
         <v>10</v>
@@ -2622,13 +2689,13 @@
         <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
         <v>6</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F13" t="n">
         <v>34</v>
       </c>
       <c r="G13" t="n">
-        <v>0.443</v>
+        <v>0.433</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
@@ -2681,28 +2748,28 @@
         <v>36.4</v>
       </c>
       <c r="J13" t="n">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>0.437</v>
       </c>
       <c r="L13" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M13" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.334</v>
+        <v>0.335</v>
       </c>
       <c r="O13" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P13" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.761</v>
+        <v>0.762</v>
       </c>
       <c r="R13" t="n">
         <v>10.5</v>
@@ -2711,7 +2778,7 @@
         <v>34.5</v>
       </c>
       <c r="T13" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="U13" t="n">
         <v>21.3</v>
@@ -2732,25 +2799,25 @@
         <v>20.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AB13" t="n">
         <v>96.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AE13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH13" t="n">
         <v>19</v>
@@ -2759,13 +2826,13 @@
         <v>24</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK13" t="n">
         <v>23</v>
       </c>
       <c r="AL13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM13" t="n">
         <v>18</v>
@@ -2774,19 +2841,19 @@
         <v>21</v>
       </c>
       <c r="AO13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR13" t="n">
         <v>20</v>
       </c>
-      <c r="AP13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>19</v>
-      </c>
       <c r="AS13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT13" t="n">
         <v>5</v>
@@ -2801,7 +2868,7 @@
         <v>28</v>
       </c>
       <c r="AX13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY13" t="n">
         <v>17</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
@@ -2941,7 +3008,7 @@
         <v>4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK14" t="n">
         <v>2</v>
@@ -2962,7 +3029,7 @@
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR14" t="n">
         <v>27</v>
@@ -2977,10 +3044,10 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX14" t="n">
         <v>9</v>
@@ -2989,10 +3056,10 @@
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -3042,13 +3109,13 @@
         <v>48.7</v>
       </c>
       <c r="I15" t="n">
-        <v>37.7</v>
+        <v>37.5</v>
       </c>
       <c r="J15" t="n">
-        <v>86.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
         <v>6.7</v>
@@ -3057,55 +3124,55 @@
         <v>19.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.346</v>
+        <v>0.345</v>
       </c>
       <c r="O15" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="P15" t="n">
-        <v>23.6</v>
+        <v>24.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.742</v>
+        <v>0.743</v>
       </c>
       <c r="R15" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.5</v>
+        <v>32.2</v>
       </c>
       <c r="T15" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U15" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V15" t="n">
         <v>12.9</v>
       </c>
       <c r="W15" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y15" t="n">
         <v>4.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="AB15" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.2</v>
+        <v>-6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3120,7 +3187,7 @@
         <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ15" t="n">
         <v>5</v>
@@ -3135,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="AN15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AQ15" t="n">
         <v>22</v>
@@ -3150,10 +3217,10 @@
         <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AT15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU15" t="n">
         <v>20</v>
@@ -3165,19 +3232,19 @@
         <v>19</v>
       </c>
       <c r="AX15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AY15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA15" t="n">
         <v>22</v>
       </c>
-      <c r="BA15" t="n">
-        <v>23</v>
-      </c>
       <c r="BB15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -3209,49 +3276,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F16" t="n">
         <v>17</v>
       </c>
       <c r="G16" t="n">
-        <v>0.721</v>
+        <v>0.717</v>
       </c>
       <c r="H16" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I16" t="n">
         <v>38.1</v>
       </c>
       <c r="J16" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K16" t="n">
         <v>0.459</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M16" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0.332</v>
+        <v>0.335</v>
       </c>
       <c r="O16" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P16" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.777</v>
+        <v>0.775</v>
       </c>
       <c r="R16" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S16" t="n">
         <v>32.4</v>
@@ -3260,13 +3327,13 @@
         <v>42.8</v>
       </c>
       <c r="U16" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V16" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W16" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X16" t="n">
         <v>4.4</v>
@@ -3275,7 +3342,7 @@
         <v>5.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AA16" t="n">
         <v>20.5</v>
@@ -3284,10 +3351,10 @@
         <v>99.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3299,10 +3366,10 @@
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ16" t="n">
         <v>18</v>
@@ -3311,7 +3378,7 @@
         <v>7</v>
       </c>
       <c r="AL16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM16" t="n">
         <v>29</v>
@@ -3320,28 +3387,28 @@
         <v>22</v>
       </c>
       <c r="AO16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ16" t="n">
         <v>5</v>
       </c>
       <c r="AR16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT16" t="n">
         <v>19</v>
       </c>
       <c r="AU16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW16" t="n">
         <v>7</v>
@@ -3350,16 +3417,16 @@
         <v>22</v>
       </c>
       <c r="AY16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ16" t="n">
         <v>7</v>
       </c>
       <c r="BA16" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BB16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC16" t="n">
         <v>8</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -3391,22 +3458,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E17" t="n">
         <v>27</v>
       </c>
       <c r="F17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G17" t="n">
-        <v>0.443</v>
+        <v>0.45</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
       </c>
       <c r="I17" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="J17" t="n">
         <v>76.09999999999999</v>
@@ -3418,7 +3485,7 @@
         <v>7</v>
       </c>
       <c r="M17" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N17" t="n">
         <v>0.344</v>
@@ -3427,10 +3494,10 @@
         <v>17.8</v>
       </c>
       <c r="P17" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.744</v>
+        <v>0.745</v>
       </c>
       <c r="R17" t="n">
         <v>9</v>
@@ -3469,16 +3536,16 @@
         <v>-2.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH17" t="n">
         <v>29</v>
@@ -3490,10 +3557,10 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM17" t="n">
         <v>20</v>
@@ -3502,13 +3569,13 @@
         <v>18</v>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3538,7 +3605,7 @@
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -3651,31 +3718,31 @@
         <v>1.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE18" t="n">
         <v>15</v>
       </c>
       <c r="AF18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
         <v>11</v>
       </c>
       <c r="AI18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ18" t="n">
         <v>25</v>
       </c>
       <c r="AK18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM18" t="n">
         <v>25</v>
@@ -3693,13 +3760,13 @@
         <v>8</v>
       </c>
       <c r="AR18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS18" t="n">
         <v>25</v>
       </c>
       <c r="AT18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
@@ -3708,7 +3775,7 @@
         <v>28</v>
       </c>
       <c r="AW18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX18" t="n">
         <v>13</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-7.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -3845,13 +3912,13 @@
         <v>28</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
         <v>23</v>
       </c>
       <c r="AJ19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK19" t="n">
         <v>25</v>
@@ -3863,19 +3930,19 @@
         <v>30</v>
       </c>
       <c r="AN19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP19" t="n">
         <v>3</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>2</v>
       </c>
       <c r="AQ19" t="n">
         <v>14</v>
       </c>
       <c r="AR19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS19" t="n">
         <v>29</v>
@@ -3884,19 +3951,19 @@
         <v>24</v>
       </c>
       <c r="AU19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW19" t="n">
         <v>8</v>
       </c>
       <c r="AX19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ19" t="n">
         <v>11</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -3940,103 +4007,103 @@
         <v>61</v>
       </c>
       <c r="E20" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G20" t="n">
-        <v>0.525</v>
+        <v>0.541</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J20" t="n">
-        <v>82.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L20" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M20" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.358</v>
+        <v>0.355</v>
       </c>
       <c r="O20" t="n">
         <v>17.1</v>
       </c>
       <c r="P20" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.77</v>
+        <v>0.762</v>
       </c>
       <c r="R20" t="n">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="S20" t="n">
         <v>31.9</v>
       </c>
       <c r="T20" t="n">
-        <v>43.5</v>
+        <v>43.8</v>
       </c>
       <c r="U20" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V20" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="W20" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X20" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z20" t="n">
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG20" t="n">
         <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ20" t="n">
         <v>19</v>
       </c>
       <c r="AK20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
         <v>23</v>
@@ -4045,7 +4112,7 @@
         <v>24</v>
       </c>
       <c r="AN20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO20" t="n">
         <v>14</v>
@@ -4054,19 +4121,19 @@
         <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU20" t="n">
         <v>16</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>15</v>
       </c>
       <c r="AV20" t="n">
         <v>7</v>
@@ -4075,16 +4142,16 @@
         <v>26</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ20" t="n">
         <v>6</v>
       </c>
       <c r="BA20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB20" t="n">
         <v>18</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4212,7 +4279,7 @@
         <v>16</v>
       </c>
       <c r="AI21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ21" t="n">
         <v>20</v>
@@ -4221,13 +4288,13 @@
         <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM21" t="n">
         <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
         <v>16</v>
@@ -4251,7 +4318,7 @@
         <v>17</v>
       </c>
       <c r="AV21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW21" t="n">
         <v>23</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -4379,10 +4446,10 @@
         <v>2.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF22" t="n">
         <v>13</v>
@@ -4391,7 +4458,7 @@
         <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="n">
         <v>7</v>
@@ -4412,16 +4479,16 @@
         <v>26</v>
       </c>
       <c r="AO22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS22" t="n">
         <v>2</v>
@@ -4433,28 +4500,28 @@
         <v>24</v>
       </c>
       <c r="AV22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW22" t="n">
         <v>22</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ22" t="n">
         <v>27</v>
       </c>
       <c r="BA22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB22" t="n">
         <v>10</v>
       </c>
       <c r="BC22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -4486,67 +4553,67 @@
         <v>62</v>
       </c>
       <c r="E23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F23" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G23" t="n">
-        <v>0.323</v>
+        <v>0.306</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.5</v>
+        <v>37.2</v>
       </c>
       <c r="J23" t="n">
         <v>81.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.458</v>
+        <v>0.455</v>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.354</v>
+        <v>0.351</v>
       </c>
       <c r="O23" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="P23" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="Q23" t="n">
         <v>0.73</v>
       </c>
       <c r="R23" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S23" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="T23" t="n">
-        <v>40.7</v>
+        <v>41</v>
       </c>
       <c r="U23" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="V23" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W23" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
         <v>21.3</v>
@@ -4555,13 +4622,13 @@
         <v>18.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.3</v>
+        <v>-5.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4573,25 +4640,25 @@
         <v>26</v>
       </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ23" t="n">
         <v>24</v>
       </c>
       <c r="AK23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AM23" t="n">
         <v>22</v>
       </c>
       <c r="AN23" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AO23" t="n">
         <v>30</v>
@@ -4606,16 +4673,16 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
       </c>
       <c r="AU23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AV23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW23" t="n">
         <v>16</v>
@@ -4624,7 +4691,7 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="n">
         <v>23</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E24" t="n">
         <v>13</v>
       </c>
       <c r="F24" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G24" t="n">
-        <v>0.21</v>
+        <v>0.213</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
@@ -4683,31 +4750,31 @@
         <v>33.1</v>
       </c>
       <c r="J24" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.41</v>
+        <v>0.411</v>
       </c>
       <c r="L24" t="n">
         <v>7.9</v>
       </c>
       <c r="M24" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="N24" t="n">
         <v>0.319</v>
       </c>
       <c r="O24" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="P24" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="R24" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S24" t="n">
         <v>31</v>
@@ -4716,7 +4783,7 @@
         <v>42.5</v>
       </c>
       <c r="U24" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V24" t="n">
         <v>18.5</v>
@@ -4731,25 +4798,25 @@
         <v>5.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AA24" t="n">
         <v>20.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>90.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>-10.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
       </c>
       <c r="AF24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG24" t="n">
         <v>29</v>
@@ -4776,10 +4843,10 @@
         <v>28</v>
       </c>
       <c r="AO24" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
@@ -4794,7 +4861,7 @@
         <v>20</v>
       </c>
       <c r="AU24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4803,16 +4870,16 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E25" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F25" t="n">
         <v>30</v>
       </c>
       <c r="G25" t="n">
-        <v>0.524</v>
+        <v>0.516</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
@@ -4868,34 +4935,34 @@
         <v>86.59999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L25" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="M25" t="n">
         <v>26.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.352</v>
+        <v>0.355</v>
       </c>
       <c r="O25" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="P25" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.774</v>
+        <v>0.775</v>
       </c>
       <c r="R25" t="n">
         <v>11</v>
       </c>
       <c r="S25" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T25" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U25" t="n">
         <v>20.6</v>
@@ -4904,31 +4971,31 @@
         <v>15.2</v>
       </c>
       <c r="W25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X25" t="n">
         <v>4.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z25" t="n">
         <v>22.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.7</v>
+        <v>105.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF25" t="n">
         <v>16</v>
@@ -4937,16 +5004,16 @@
         <v>16</v>
       </c>
       <c r="AH25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI25" t="n">
         <v>2</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL25" t="n">
         <v>7</v>
@@ -4955,7 +5022,7 @@
         <v>7</v>
       </c>
       <c r="AN25" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
         <v>16</v>
@@ -4967,40 +5034,40 @@
         <v>6</v>
       </c>
       <c r="AR25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS25" t="n">
         <v>18</v>
       </c>
       <c r="AT25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV25" t="n">
         <v>25</v>
       </c>
       <c r="AW25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
         <v>5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB25" t="n">
         <v>3</v>
       </c>
       <c r="BC25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>5.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE26" t="n">
         <v>4</v>
@@ -5122,10 +5189,10 @@
         <v>5</v>
       </c>
       <c r="AI26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK26" t="n">
         <v>19</v>
@@ -5137,7 +5204,7 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
         <v>25</v>
@@ -5167,7 +5234,7 @@
         <v>25</v>
       </c>
       <c r="AX26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
         <v>21</v>
       </c>
       <c r="F27" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G27" t="n">
-        <v>0.35</v>
+        <v>0.356</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
@@ -5229,34 +5296,34 @@
         <v>36.2</v>
       </c>
       <c r="J27" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="K27" t="n">
         <v>0.45</v>
       </c>
       <c r="L27" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="M27" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.329</v>
+        <v>0.328</v>
       </c>
       <c r="O27" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="P27" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="R27" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S27" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="T27" t="n">
         <v>44.7</v>
@@ -5265,13 +5332,13 @@
         <v>19.5</v>
       </c>
       <c r="V27" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="W27" t="n">
         <v>6.5</v>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y27" t="n">
         <v>6</v>
@@ -5283,13 +5350,13 @@
         <v>24.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.5</v>
+        <v>100.3</v>
       </c>
       <c r="AC27" t="n">
         <v>-4</v>
       </c>
       <c r="AD27" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5301,7 +5368,7 @@
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
@@ -5310,16 +5377,16 @@
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM27" t="n">
         <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5331,13 +5398,13 @@
         <v>7</v>
       </c>
       <c r="AR27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT27" t="n">
         <v>8</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>7</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
@@ -5349,10 +5416,10 @@
         <v>27</v>
       </c>
       <c r="AX27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ27" t="n">
         <v>18</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -5408,34 +5475,34 @@
         <v>48.8</v>
       </c>
       <c r="I28" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J28" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="K28" t="n">
         <v>0.455</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
         <v>22.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="O28" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="P28" t="n">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.771</v>
+        <v>0.772</v>
       </c>
       <c r="R28" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S28" t="n">
         <v>33.8</v>
@@ -5447,13 +5514,13 @@
         <v>24.1</v>
       </c>
       <c r="V28" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="W28" t="n">
         <v>7.7</v>
       </c>
       <c r="X28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y28" t="n">
         <v>4.7</v>
@@ -5462,16 +5529,16 @@
         <v>19.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>101.1</v>
+        <v>100.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE28" t="n">
         <v>11</v>
@@ -5480,19 +5547,19 @@
         <v>7</v>
       </c>
       <c r="AG28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5501,22 +5568,22 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR28" t="n">
         <v>26</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
         <v>13</v>
@@ -5525,10 +5592,10 @@
         <v>6</v>
       </c>
       <c r="AV28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW28" t="n">
         <v>14</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>15</v>
       </c>
       <c r="AX28" t="n">
         <v>7</v>
@@ -5540,13 +5607,13 @@
         <v>10</v>
       </c>
       <c r="BA28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E29" t="n">
         <v>38</v>
       </c>
       <c r="F29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G29" t="n">
-        <v>0.613</v>
+        <v>0.623</v>
       </c>
       <c r="H29" t="n">
         <v>48.5</v>
@@ -5593,46 +5660,46 @@
         <v>38.1</v>
       </c>
       <c r="J29" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K29" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L29" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="N29" t="n">
         <v>0.347</v>
       </c>
       <c r="O29" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="P29" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.785</v>
+        <v>0.784</v>
       </c>
       <c r="R29" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S29" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T29" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U29" t="n">
         <v>20.7</v>
       </c>
       <c r="V29" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W29" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X29" t="n">
         <v>4.5</v>
@@ -5644,37 +5711,37 @@
         <v>21.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>104.4</v>
+        <v>104.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE29" t="n">
         <v>10</v>
       </c>
       <c r="AF29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG29" t="n">
         <v>9</v>
       </c>
-      <c r="AG29" t="n">
-        <v>10</v>
-      </c>
       <c r="AH29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ29" t="n">
         <v>13</v>
       </c>
       <c r="AK29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL29" t="n">
         <v>9</v>
@@ -5683,31 +5750,31 @@
         <v>9</v>
       </c>
       <c r="AN29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP29" t="n">
         <v>5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
       </c>
       <c r="AT29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU29" t="n">
         <v>21</v>
       </c>
       <c r="AV29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW29" t="n">
         <v>12</v>
@@ -5719,10 +5786,10 @@
         <v>19</v>
       </c>
       <c r="AZ29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB29" t="n">
         <v>5</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -5757,61 +5824,61 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F30" t="n">
         <v>36</v>
       </c>
       <c r="G30" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="J30" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L30" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M30" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="N30" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O30" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="P30" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.731</v>
+        <v>0.732</v>
       </c>
       <c r="R30" t="n">
         <v>11.8</v>
       </c>
       <c r="S30" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T30" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U30" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V30" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W30" t="n">
         <v>7.3</v>
@@ -5826,19 +5893,19 @@
         <v>19.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>95.2</v>
+        <v>95.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AE30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF30" t="n">
         <v>22</v>
@@ -5850,13 +5917,13 @@
         <v>30</v>
       </c>
       <c r="AI30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ30" t="n">
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL30" t="n">
         <v>17</v>
@@ -5865,10 +5932,10 @@
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP30" t="n">
         <v>16</v>
@@ -5877,13 +5944,13 @@
         <v>25</v>
       </c>
       <c r="AR30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU30" t="n">
         <v>28</v>
@@ -5892,16 +5959,16 @@
         <v>26</v>
       </c>
       <c r="AW30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX30" t="n">
         <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA30" t="n">
         <v>25</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F31" t="n">
         <v>27</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
@@ -5960,28 +6027,28 @@
         <v>82.5</v>
       </c>
       <c r="K31" t="n">
-        <v>0.465</v>
+        <v>0.466</v>
       </c>
       <c r="L31" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M31" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O31" t="n">
         <v>15.9</v>
       </c>
       <c r="P31" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.746</v>
+        <v>0.744</v>
       </c>
       <c r="R31" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S31" t="n">
         <v>33.5</v>
@@ -6017,7 +6084,7 @@
         <v>0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6029,7 +6096,7 @@
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI31" t="n">
         <v>6</v>
@@ -6047,7 +6114,7 @@
         <v>27</v>
       </c>
       <c r="AN31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO31" t="n">
         <v>27</v>
@@ -6056,10 +6123,10 @@
         <v>24</v>
       </c>
       <c r="AQ31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS31" t="n">
         <v>9</v>
@@ -6074,7 +6141,7 @@
         <v>24</v>
       </c>
       <c r="AW31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX31" t="n">
         <v>15</v>
@@ -6092,7 +6159,7 @@
         <v>19</v>
       </c>
       <c r="BC31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-6-2014-15</t>
+          <t>2015-03-06</t>
         </is>
       </c>
     </row>
